--- a/packages/scraping-pipeline/__tests__/fixtures/statement-of-vote-sample.xlsx
+++ b/packages/scraping-pipeline/__tests__/fixtures/statement-of-vote-sample.xlsx
@@ -1059,6 +1059,1277 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>7103</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1553</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>265371</v>
+      </c>
+      <c r="C21" s="2">
+        <v>123132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3264</v>
+      </c>
+      <c r="C24" s="2">
+        <v>5111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2">
+        <v>34534</v>
+      </c>
+      <c r="C27" s="2">
+        <v>54137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2">
+        <v>98417</v>
+      </c>
+      <c r="C30" s="2">
+        <v>120668</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1930</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2">
+        <v>29541</v>
+      </c>
+      <c r="C36" s="2">
+        <v>18257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16711</v>
+      </c>
+      <c r="C39" s="2">
+        <v>13158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2">
+        <v>3382</v>
+      </c>
+      <c r="C42" s="2">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2">
+        <v>69706</v>
+      </c>
+      <c r="C45" s="2">
+        <v>119006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="2">
+        <v>9389</v>
+      </c>
+      <c r="C48" s="2">
+        <v>17523</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2">
+        <v>9771</v>
+      </c>
+      <c r="C51" s="2">
+        <v>10360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1444</v>
+      </c>
+      <c r="C54" s="2">
+        <v>7726</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1620053</v>
+      </c>
+      <c r="C57" s="2">
+        <v>769174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="2">
+        <v>13283</v>
+      </c>
+      <c r="C60" s="2">
+        <v>23678</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="2">
+        <v>95289</v>
+      </c>
+      <c r="C63" s="2">
+        <v>23775</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="2">
+        <v>2944</v>
+      </c>
+      <c r="C66" s="2">
+        <v>4896</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" s="2">
+        <v>19031</v>
+      </c>
+      <c r="C69" s="2">
+        <v>11363</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="2">
+        <v>25200</v>
+      </c>
+      <c r="C72" s="2">
+        <v>30073</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="2">
+        <v>687</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B78" s="2">
+        <v>2493</v>
+      </c>
+      <c r="C78" s="2">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" s="2">
+        <v>65262</v>
+      </c>
+      <c r="C81" s="2">
+        <v>36867</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="2">
+        <v>32437</v>
+      </c>
+      <c r="C84" s="2">
+        <v>17671</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" s="2">
+        <v>26655</v>
+      </c>
+      <c r="C87" s="2">
+        <v>24082</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="2">
+        <v>464206</v>
+      </c>
+      <c r="C90" s="2">
+        <v>492734</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B93" s="2">
+        <v>73619</v>
+      </c>
+      <c r="C93" s="2">
+        <v>108450</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B96" s="2">
+        <v>3083</v>
+      </c>
+      <c r="C96" s="2">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" s="2">
+        <v>285000</v>
+      </c>
+      <c r="C99" s="2">
+        <v>310901</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B102" s="2">
+        <v>274680</v>
+      </c>
+      <c r="C102" s="2">
+        <v>202933</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B105" s="2">
+        <v>10428</v>
+      </c>
+      <c r="C105" s="2">
+        <v>9150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" s="2">
+        <v>215391</v>
+      </c>
+      <c r="C108" s="2">
+        <v>239109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B111" s="2">
+        <v>574121</v>
+      </c>
+      <c r="C111" s="2">
+        <v>455107</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B114" s="2">
+        <v>257402</v>
+      </c>
+      <c r="C114" s="2">
+        <v>44064</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B117" s="2">
+        <v>85498</v>
+      </c>
+      <c r="C117" s="2">
+        <v>91827</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B120" s="2">
+        <v>61166</v>
+      </c>
+      <c r="C120" s="2">
+        <v>58464</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B123" s="2">
+        <v>185599</v>
+      </c>
+      <c r="C123" s="2">
+        <v>61918</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B126" s="2">
+        <v>80648</v>
+      </c>
+      <c r="C126" s="2">
+        <v>54726</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B129" s="2">
+        <v>379377</v>
+      </c>
+      <c r="C129" s="2">
+        <v>162518</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B132" s="2">
+        <v>79117</v>
+      </c>
+      <c r="C132" s="2">
+        <v>25052</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B135" s="2">
+        <v>18607</v>
+      </c>
+      <c r="C135" s="2">
+        <v>49913</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B138" s="2">
+        <v>529</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B141" s="2">
+        <v>6326</v>
+      </c>
+      <c r="C141" s="2">
+        <v>11397</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B144" s="2">
+        <v>77769</v>
+      </c>
+      <c r="C144" s="2">
+        <v>52850</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B147" s="2">
+        <v>140041</v>
+      </c>
+      <c r="C147" s="2">
+        <v>57413</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B150" s="2">
+        <v>55311</v>
+      </c>
+      <c r="C150" s="2">
+        <v>75656</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B153" s="2">
+        <v>9082</v>
+      </c>
+      <c r="C153" s="2">
+        <v>19024</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B156" s="2">
+        <v>5024</v>
+      </c>
+      <c r="C156" s="2">
+        <v>15607</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B159" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C159" s="2">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B162" s="2">
+        <v>33273</v>
+      </c>
+      <c r="C162" s="2">
+        <v>58053</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B165" s="2">
+        <v>8471</v>
+      </c>
+      <c r="C165" s="2">
+        <v>14759</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B168" s="2">
+        <v>153226</v>
+      </c>
+      <c r="C168" s="2">
+        <v>127709</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B171" s="2">
+        <v>44328</v>
+      </c>
+      <c r="C171" s="2">
+        <v>22807</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B174" s="2">
+        <v>6534</v>
+      </c>
+      <c r="C174" s="2">
+        <v>13097</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B177" s="2">
+        <v>6470104</v>
+      </c>
+      <c r="C177" s="2">
+        <v>4462914</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" s="3" customFormat="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" s="11" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:3" s="3" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="8"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.5"/>
   <pageSetup firstPageNumber="19" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
